--- a/public/exports/29189420.xlsx
+++ b/public/exports/29189420.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020300</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -15064,12 +15064,12 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020312</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15439,7 +15439,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -16339,12 +16339,12 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020327</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020292</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -19939,12 +19939,12 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -20014,12 +20014,12 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -20089,12 +20089,12 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -20164,12 +20164,12 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -20239,12 +20239,12 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -20314,12 +20314,12 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -20389,12 +20389,12 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -20464,12 +20464,12 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -20539,12 +20539,12 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -20614,12 +20614,12 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -30064,7 +30064,7 @@
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477935</t>
+          <t xml:space="preserve">311477990</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
@@ -38914,7 +38914,7 @@
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555497</t>
+          <t xml:space="preserve">311555498</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
@@ -42139,7 +42139,7 @@
       </c>
       <c r="K562" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568868</t>
+          <t xml:space="preserve">311568869</t>
         </is>
       </c>
       <c r="L562" t="inlineStr">
@@ -42439,7 +42439,7 @@
       </c>
       <c r="K566" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568866</t>
+          <t xml:space="preserve">311568869</t>
         </is>
       </c>
       <c r="L566" t="inlineStr">
@@ -46339,12 +46339,12 @@
       </c>
       <c r="K618" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803905</t>
+          <t xml:space="preserve">311803934</t>
         </is>
       </c>
       <c r="L618" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M618" t="inlineStr">

--- a/public/exports/29189420.xlsx
+++ b/public/exports/29189420.xlsx
@@ -19864,12 +19864,12 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -19939,12 +19939,12 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -20014,12 +20014,12 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -20089,12 +20089,12 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -20164,12 +20164,12 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -20239,12 +20239,12 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -20314,12 +20314,12 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -20389,12 +20389,12 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -20464,12 +20464,12 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -20539,12 +20539,12 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -20614,12 +20614,12 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -30064,7 +30064,7 @@
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477990</t>
+          <t xml:space="preserve">311477935</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
@@ -38914,7 +38914,7 @@
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555498</t>
+          <t xml:space="preserve">311555497</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
@@ -41914,7 +41914,7 @@
       </c>
       <c r="K559" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568269</t>
+          <t xml:space="preserve">311568275</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
@@ -42514,7 +42514,7 @@
       </c>
       <c r="K567" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568867</t>
+          <t xml:space="preserve">311568869</t>
         </is>
       </c>
       <c r="L567" t="inlineStr">
@@ -46339,12 +46339,12 @@
       </c>
       <c r="K618" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803934</t>
+          <t xml:space="preserve">311803905</t>
         </is>
       </c>
       <c r="L618" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M618" t="inlineStr">
